--- a/421-contenu-fhir---mise-à-jour-de-lévènement/ig/ValueSet-tddui-observation-type.xlsx
+++ b/421-contenu-fhir---mise-à-jour-de-lévènement/ig/ValueSet-tddui-observation-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T13:39:19+00:00</t>
+    <t>2026-02-27T14:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/421-contenu-fhir---mise-à-jour-de-lévènement/ig/ValueSet-tddui-observation-type.xlsx
+++ b/421-contenu-fhir---mise-à-jour-de-lévènement/ig/ValueSet-tddui-observation-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T14:39:40+00:00</t>
+    <t>2026-02-27T15:25:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/421-contenu-fhir---mise-à-jour-de-lévènement/ig/ValueSet-tddui-observation-type.xlsx
+++ b/421-contenu-fhir---mise-à-jour-de-lévènement/ig/ValueSet-tddui-observation-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T15:25:53+00:00</t>
+    <t>2026-02-27T15:59:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
